--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N85_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N85_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.164951507814813</v>
+        <v>1.489304620019907</v>
       </c>
       <c r="D2" t="n">
-        <v>6.790057299714736</v>
+        <v>1.103384311203645</v>
       </c>
       <c r="E2" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F2" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.08679276123039</v>
+        <v>3.751603823699939</v>
       </c>
       <c r="D3" t="n">
-        <v>5.879215415313623</v>
+        <v>0.9553725049884637</v>
       </c>
       <c r="E3" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F3" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.17741035871079</v>
+        <v>3.441329183290504</v>
       </c>
       <c r="D4" t="n">
-        <v>17.15097303896995</v>
+        <v>2.787033118832617</v>
       </c>
       <c r="E4" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F4" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>5.672989578637273</v>
+        <v>0.9218608065285568</v>
       </c>
       <c r="D5" t="n">
-        <v>8.57485279097758</v>
+        <v>1.393413578533857</v>
       </c>
       <c r="E5" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F5" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.27624183655663</v>
+        <v>5.732389298440452</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29301346863103</v>
+        <v>5.572614688652543</v>
       </c>
       <c r="E6" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F6" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.567316414823138</v>
+        <v>1.55468891740876</v>
       </c>
       <c r="D7" t="n">
-        <v>9.73889387329158</v>
+        <v>1.582570254409882</v>
       </c>
       <c r="E7" t="n">
-        <v>10.26988960224457</v>
+        <v>1.668857060364743</v>
       </c>
       <c r="F7" t="n">
-        <v>9.889744733184413</v>
+        <v>1.607083519142467</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
